--- a/output/pdf_financials_xlsx/CYTO.H.xlsx
+++ b/output/pdf_financials_xlsx/CYTO.H.xlsx
@@ -2773,16 +2773,16 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.413785</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.284199</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>4.21102</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>5.051176</v>
       </c>
     </row>
     <row r="93">
@@ -4600,7 +4600,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -5378,7 +5382,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -5834,7 +5842,11 @@
           <t>Warrant reserve 4</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -6250,7 +6262,11 @@
           <t>Warrant reserve 5</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CYTO.H.xlsx
+++ b/output/pdf_financials_xlsx/CYTO.H.xlsx
@@ -702,19 +702,19 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000306</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.086038</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.003786</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.14216</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.004519</v>
       </c>
     </row>
     <row r="13">
@@ -1103,19 +1103,19 @@
         <v>-0.003446</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.042378</v>
+        <v>-0.042684</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.706206</v>
+        <v>-0.7922439999999999</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.635417</v>
+        <v>-4.639203</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-7.862699</v>
+        <v>-8.004859</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-7.862699</v>
+        <v>-7.867218</v>
       </c>
     </row>
     <row r="28">
@@ -1153,19 +1153,19 @@
         <v>-0.003446</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.042378</v>
+        <v>-0.042684</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.706206</v>
+        <v>-0.7922439999999999</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.12259</v>
+        <v>-4.126376</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-7.155443</v>
+        <v>-7.297603</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-7.183954</v>
+        <v>-7.188473</v>
       </c>
     </row>
     <row r="30">
@@ -1284,10 +1284,10 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.024963</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.06950199999999999</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.031682</v>
@@ -1334,10 +1334,10 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.7753060000000001</v>
+        <v>0.800269</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>5.343692</v>
+        <v>5.413194</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>5.460763</v>
@@ -3564,13 +3564,13 @@
         <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.211461</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.261197</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.215026</v>
       </c>
     </row>
     <row r="125">
@@ -3589,13 +3589,13 @@
         <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.211461</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.261197</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.215026</v>
       </c>
     </row>
     <row r="126">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -7602,7 +7602,11 @@
           <t>Principal lease payments</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -10010,7 +10014,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12228,7 +12232,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">

--- a/output/pdf_financials_xlsx/CYTO.H.xlsx
+++ b/output/pdf_financials_xlsx/CYTO.H.xlsx
@@ -2058,13 +2058,13 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.02378</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.002825</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.009209</v>
       </c>
       <c r="F64" s="3" t="n">
         <v>0</v>
@@ -2139,13 +2139,13 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.409626</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.259649</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.111361</v>
       </c>
     </row>
     <row r="68">
